--- a/mapping/SB_DWH/Mapping_DIM_CLOS_APPLICATION.xlsx
+++ b/mapping/SB_DWH/Mapping_DIM_CLOS_APPLICATION.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variable" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$5:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Mapping'!$A$6:$E$71</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -230,7 +230,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -307,9 +307,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -362,9 +359,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -693,7 +687,7 @@
     <col width="29.6640625" customWidth="1" style="7" min="1" max="1"/>
     <col width="20.5" customWidth="1" style="7" min="2" max="2"/>
     <col width="27.6640625" customWidth="1" style="1" min="3" max="3"/>
-    <col width="37" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="52.1640625" customWidth="1" style="2" min="4" max="4"/>
     <col width="50.33203125" customWidth="1" style="7" min="5" max="5"/>
     <col width="48.5" customWidth="1" style="2" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="7" min="7" max="16384"/>
@@ -710,12 +704,12 @@
           <t>DIM_CLOS_APPLICATION</t>
         </is>
       </c>
-      <c r="E1" s="43" t="inlineStr">
+      <c r="E1" s="42" t="inlineStr">
         <is>
           <t>NG_SB_CLOS_EXTTABLE AS A</t>
         </is>
       </c>
-      <c r="F1" s="43" t="n"/>
+      <c r="F1" s="42" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -728,66 +722,72 @@
           <t>Bảng chiều hồ sơ tín dụng CLOS, driving từ NG_SB_CLOS_EXTTABLE, bổ sung thuộc tính từ APPROVAL/ENTRY_EXIT/CREDITINFO_COMM/CUST_INFO/CUST_INFO_LEGAL</t>
         </is>
       </c>
-      <c r="E2" s="43" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>NG_SB_CLOS_APPROVAL AS B</t>
         </is>
       </c>
-      <c r="F2" s="43" t="n"/>
+      <c r="F2" s="42" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Primary Key</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>Bao gồm các trường màu đỏ</t>
-        </is>
-      </c>
-      <c r="E3" s="43" t="inlineStr">
+          <t>DIMENSION_KEY</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
         <is>
           <t>NG_SB_CLOS_ENTRY_EXIT AS C</t>
         </is>
       </c>
-      <c r="F3" s="43" t="n"/>
+      <c r="F3" s="42" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="E4" s="43" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Business Key</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>NG_SB_CLOS_CREDITINFO_COMM AS D</t>
         </is>
       </c>
-      <c r="F4" s="43" t="n"/>
+      <c r="F4" s="42" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="6" t="n"/>
-      <c r="C5" s="44" t="n"/>
-      <c r="D5" s="44" t="n"/>
-      <c r="E5" s="43" t="inlineStr">
+      <c r="E5" s="42" t="inlineStr">
         <is>
           <t>NG_SB_CLOS_CUST_INFO AS E</t>
         </is>
       </c>
-      <c r="F5" s="43" t="n"/>
+      <c r="F5" s="42" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="6" t="n"/>
-      <c r="C6" s="44" t="n"/>
-      <c r="D6" s="44" t="n"/>
-      <c r="E6" s="43" t="inlineStr">
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="43" t="n"/>
+      <c r="E6" s="42" t="inlineStr">
         <is>
           <t>NG_SB_CLOS_CUST_INFO_LEGAL AS F</t>
         </is>
       </c>
-      <c r="F6" s="43" t="n"/>
-    </row>
-    <row r="7" ht="17" customHeight="1">
+      <c r="F6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="19.5" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Column name</t>
@@ -827,18 +827,18 @@
       <c r="E8" s="24" t="n"/>
       <c r="F8" s="24" t="n"/>
     </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="26" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>DIMENSION_KEY</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C9" s="31" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>Surrogate Key</t>
         </is>
@@ -853,20 +853,20 @@
           <t>Sinh bằng Oracle sequence tại SB_DWH</t>
         </is>
       </c>
-      <c r="F9" s="31" t="n"/>
-    </row>
-    <row r="10" ht="17" customFormat="1" customHeight="1" s="5">
-      <c r="A10" s="45" t="inlineStr">
+      <c r="F9" s="30" t="n"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B10" s="26" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>Khóa tham chiếu DIM_CLOS_APPLICATION</t>
         </is>
@@ -881,20 +881,20 @@
           <t>Sinh bằng Oracle sequence tại SB_DWH</t>
         </is>
       </c>
-      <c r="F10" s="31" t="n"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="F10" s="30" t="n"/>
+    </row>
+    <row r="11" ht="30" customFormat="1" customHeight="1" s="5">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>WI_NAME</t>
         </is>
       </c>
-      <c r="B11" s="27" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C11" s="31" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng CLOS</t>
         </is>
@@ -909,20 +909,20 @@
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F11" s="31" t="n"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="F11" s="30" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>LOANCASEID</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Mã khoản vay</t>
         </is>
@@ -937,20 +937,20 @@
           <t>A.LOANCASEID</t>
         </is>
       </c>
-      <c r="F12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="F12" s="30" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>STREAM</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Luồng nghiệp vụ</t>
         </is>
@@ -965,20 +965,20 @@
           <t>B.STREAM</t>
         </is>
       </c>
-      <c r="F13" s="31" t="n"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="F13" s="30" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="36" t="inlineStr">
         <is>
           <t>CREDIT_PROFILE</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C14" s="31" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>Cấp tín dụng</t>
         </is>
@@ -993,20 +993,20 @@
           <t>A.CREDIT_PROFILE</t>
         </is>
       </c>
-      <c r="F14" s="31" t="n"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="F14" s="30" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>CREATE_EMPLOYEE_CODE</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>Mã CRO</t>
         </is>
@@ -1021,20 +1021,20 @@
           <t>A.EMPLOYEE_CODE</t>
         </is>
       </c>
-      <c r="F15" s="31" t="n"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="45" t="inlineStr">
+      <c r="F15" s="30" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="36" t="inlineStr">
         <is>
           <t>CREATE_EMPLOYEE_NAME</t>
         </is>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(225)</t>
         </is>
       </c>
-      <c r="C16" s="31" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Tên CRO</t>
         </is>
@@ -1049,20 +1049,20 @@
           <t>A.EMPLOYEE_NAME</t>
         </is>
       </c>
-      <c r="F16" s="31" t="n"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="45" t="inlineStr">
+      <c r="F16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t>CREATION_DATE</t>
         </is>
       </c>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C17" s="31" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>Ngày khởi tạo hồ sơ</t>
         </is>
@@ -1077,20 +1077,20 @@
           <t>TRUNC(MIN(C.ENTRYDATE)) theo A.WI_NAME</t>
         </is>
       </c>
-      <c r="F17" s="31" t="n"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="F17" s="30" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="36" t="inlineStr">
         <is>
           <t>APP_GRP</t>
         </is>
       </c>
-      <c r="B18" s="27" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Cấp thẩm quyền phê duyệt</t>
         </is>
@@ -1105,20 +1105,20 @@
           <t>B.APP_GRP</t>
         </is>
       </c>
-      <c r="F18" s="31" t="n"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="45" t="inlineStr">
+      <c r="F18" s="30" t="n"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="36" t="inlineStr">
         <is>
           <t>HAVE_ANY_DEVIATION</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C19" s="31" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Có ngoại lệ/độ lệch</t>
         </is>
@@ -1133,20 +1133,20 @@
           <t>D.HAVE_ANY_DEVIATION</t>
         </is>
       </c>
-      <c r="F19" s="31" t="n"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="45" t="inlineStr">
+      <c r="F19" s="30" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="36" t="inlineStr">
         <is>
           <t>ZONE</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B20" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Khu vực/vùng quản lý</t>
         </is>
@@ -1161,20 +1161,20 @@
           <t>E.ZONEE</t>
         </is>
       </c>
-      <c r="F20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="45" t="inlineStr">
+      <c r="F20" s="30" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="36" t="inlineStr">
         <is>
           <t>LOAN_PURPOSE</t>
         </is>
       </c>
-      <c r="B21" s="27" t="inlineStr">
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C21" s="31" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Mục đích vay</t>
         </is>
@@ -1189,20 +1189,20 @@
           <t>E.LOAN_PURPOSE</t>
         </is>
       </c>
-      <c r="F21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="F21" s="30" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C22" s="31" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>Email liên hệ</t>
         </is>
@@ -1217,20 +1217,20 @@
           <t>E.EMAIL</t>
         </is>
       </c>
-      <c r="F22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="45" t="inlineStr">
+      <c r="F22" s="30" t="n"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="36" t="inlineStr">
         <is>
           <t>DISTANCE_BRANCH_CUSTOMER</t>
         </is>
       </c>
-      <c r="B23" s="27" t="inlineStr">
+      <c r="B23" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C23" s="31" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>Khoảng cách KH-chi nhánh</t>
         </is>
@@ -1245,20 +1245,20 @@
           <t>E.DISTANCE_BRANCH_CUSTOMER</t>
         </is>
       </c>
-      <c r="F23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="45" t="inlineStr">
+      <c r="F23" s="30" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>PRODUCT_LINE</t>
         </is>
       </c>
-      <c r="B24" s="27" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C24" s="31" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>Dòng sản phẩm tự khai</t>
         </is>
@@ -1273,20 +1273,20 @@
           <t>E.PRODUCT_LINE</t>
         </is>
       </c>
-      <c r="F24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="45" t="inlineStr">
+      <c r="F24" s="30" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>SUB_PRODUCT</t>
         </is>
       </c>
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(255)</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C25" s="30" t="inlineStr">
         <is>
           <t>Sản phẩm vay chi tiết</t>
         </is>
@@ -1301,20 +1301,20 @@
           <t>E.SUB_PRODUCT</t>
         </is>
       </c>
-      <c r="F25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="45" t="inlineStr">
-        <is>
-          <t>ID_NUMBER</t>
-        </is>
-      </c>
-      <c r="B26" s="27" t="inlineStr">
+      <c r="F25" s="30" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="36" t="inlineStr">
+        <is>
+          <t>CUSTOMER_CODE</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>Số ĐKKD/CMND khách hàng chính</t>
         </is>
@@ -1329,20 +1329,20 @@
           <t>F.ID_NUMBER</t>
         </is>
       </c>
-      <c r="F26" s="31" t="n"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="45" t="inlineStr">
+      <c r="F26" s="30" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>CHANNEL</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C27" s="31" t="inlineStr">
+      <c r="C27" s="30" t="inlineStr">
         <is>
           <t>Kênh nộp hồ sơ</t>
         </is>
@@ -1357,27 +1357,27 @@
           <t>A.CHANNEL</t>
         </is>
       </c>
-      <c r="F27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="45" t="inlineStr">
+      <c r="F27" s="30" t="n"/>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>EFF_DATE</t>
         </is>
       </c>
-      <c r="B28" s="27" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C28" s="31" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>Ngày hiệu lực bản ghi</t>
         </is>
       </c>
       <c r="D28" s="17" t="inlineStr">
         <is>
-          <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2) — CDC: so sánh bản ghi cũ/mới của A tại mỗi lần ETL chạy</t>
+          <t>Ngày bắt đầu hiệu lực của phiên bản bản ghi (SCD Type 2)</t>
         </is>
       </c>
       <c r="E28" s="17" t="inlineStr">
@@ -1385,20 +1385,20 @@
           <t>v_batch_date</t>
         </is>
       </c>
-      <c r="F28" s="31" t="n"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="45" t="inlineStr">
+      <c r="F28" s="30" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>EXP_DATE</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C29" s="31" t="inlineStr">
+      <c r="C29" s="30" t="inlineStr">
         <is>
           <t>Ngày hết hiệu lực bản ghi</t>
         </is>
@@ -1413,14 +1413,14 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="F29" s="31" t="n"/>
-    </row>
-    <row r="30" ht="17" customHeight="1"/>
+      <c r="F29" s="30" t="n"/>
+    </row>
+    <row r="30" ht="51" customHeight="1"/>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="18" t="n"/>
       <c r="B31" s="18" t="n"/>
       <c r="C31" s="18" t="n"/>
-      <c r="D31" s="46" t="inlineStr">
+      <c r="D31" s="44" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
@@ -1428,10 +1428,10 @@
       <c r="E31" s="18" t="n"/>
       <c r="F31" s="18" t="n"/>
     </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="30" t="n"/>
-      <c r="B32" s="30" t="n"/>
-      <c r="C32" s="31" t="n"/>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="29" t="n"/>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="30" t="n"/>
       <c r="D32" s="17" t="n"/>
       <c r="E32" s="14" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
       </c>
       <c r="F32" s="8" t="n"/>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="30" t="n"/>
-      <c r="B33" s="30" t="n"/>
-      <c r="C33" s="31" t="n"/>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="30" t="n"/>
       <c r="D33" s="17" t="n"/>
       <c r="E33" s="14" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
       </c>
       <c r="F33" s="8" t="n"/>
     </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="30" t="n"/>
-      <c r="B34" s="30" t="n"/>
-      <c r="C34" s="31" t="n"/>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="29" t="n"/>
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="30" t="n"/>
       <c r="D34" s="17" t="n"/>
       <c r="E34" s="14" t="inlineStr">
         <is>
@@ -1464,10 +1464,10 @@
       </c>
       <c r="F34" s="8" t="n"/>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="30" t="n"/>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="31" t="n"/>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="29" t="n"/>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="30" t="n"/>
       <c r="D35" s="17" t="n"/>
       <c r="E35" s="14" t="inlineStr">
         <is>
@@ -1492,9 +1492,9 @@
     <row r="49" ht="17" customHeight="1"/>
     <row r="50" ht="17" customHeight="1"/>
     <row r="51" ht="17" customHeight="1"/>
-    <row r="52" ht="119" customHeight="1"/>
+    <row r="52" ht="17" customHeight="1"/>
     <row r="53" ht="119" customHeight="1"/>
-    <row r="54" ht="17" customHeight="1"/>
+    <row r="54" ht="119" customHeight="1"/>
     <row r="55" ht="17" customHeight="1"/>
     <row r="56" ht="17" customHeight="1"/>
     <row r="57" ht="17" customHeight="1"/>
@@ -1503,19 +1503,17 @@
     <row r="60" ht="17" customHeight="1"/>
     <row r="61" ht="17" customHeight="1"/>
     <row r="62" ht="17" customHeight="1"/>
-    <row r="63" ht="17" customFormat="1" customHeight="1" s="15"/>
-    <row r="64" ht="17" customHeight="1"/>
+    <row r="63" ht="17" customHeight="1"/>
+    <row r="64" ht="17" customFormat="1" customHeight="1" s="15"/>
     <row r="65" ht="17" customHeight="1"/>
     <row r="66" ht="17" customHeight="1"/>
     <row r="67" ht="17" customHeight="1"/>
     <row r="68" ht="17" customHeight="1"/>
-    <row r="69" ht="16" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71"/>
-    <row r="72"/>
-    <row r="74"/>
+    <row r="69" ht="17" customHeight="1"/>
+    <row r="70" ht="16" customHeight="1"/>
+    <row r="71" ht="17" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A5:E70"/>
+  <autoFilter ref="A6:E71"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter>
